--- a/forms/trg/Formulir_TRG_mdrg.xlsx
+++ b/forms/trg/Formulir_TRG_mdrg.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B26)</f>
+        <f>COUNTA(Anggota!B5:B27)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F26)</f>
+        <f>COUNTA(Anggota!F5:F27)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,27 +925,31 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Sabbar Dahham Sabbar, MSBA</t>
+          <t>Prof. Dr. Abdul Razak Munir, SE, M.Si, M.Mktg, C.MP, CMA.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>257530</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57193749825</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -958,12 +962,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Musran Munizu, SE, M.Si, MAP, CIPM</t>
+          <t>Dr. Sabbar Dahham Sabbar, MSBA</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -977,11 +981,7 @@
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n"/>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>5976956</t>
-        </is>
-      </c>
+      <c r="K6" s="12" t="n"/>
       <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
@@ -995,17 +995,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Omar (Mohammad Ali) Alqudah</t>
+          <t>Prof. Dr. Musran Munizu, SE, M.Si, MAP, CIPM</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Irbid National University Jordan</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E7" s="11" t="n"/>
@@ -1014,7 +1014,11 @@
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>5976956</t>
+        </is>
+      </c>
       <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
         <is>
@@ -1028,25 +1032,25 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Romi Setiawan, SE, MSM.</t>
+          <t>Dr. Omar (Mohammad Ali) Alqudah</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Irbid National University Jordan</t>
+        </is>
+      </c>
       <c r="E8" s="11" t="n"/>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-2761-4403</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
@@ -1061,25 +1065,25 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Rianda Ridho Hafiz Thaha, SE, MBA</t>
+          <t>Romi Setiawan, SE, MSM.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n"/>
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-2761-4403</t>
+        </is>
+      </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="12" t="n"/>
       <c r="M9" s="11" t="inlineStr">
@@ -1094,31 +1098,27 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Andi Raina Ananda Herdiana, SE, M.Sc</t>
+          <t>Rianda Ridho Hafiz Thaha, SE, MBA</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E10" s="11" t="n"/>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>0009-0000-0589-5104</t>
-        </is>
-      </c>
+      <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>58571312300</t>
-        </is>
-      </c>
+      <c r="L10" s="12" t="n"/>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Insany Fitri Nurqamar, S.E., M.M.</t>
+          <t>Andi Raina Ananda Herdiana, SE, M.Sc</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -1145,9 +1145,17 @@
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>0009-0000-0589-5104</t>
+        </is>
+      </c>
       <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>58571312300</t>
+        </is>
+      </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1160,33 +1168,21 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Fahrina Mustafa, SE., M. Si</t>
+          <t>Insany Fitri Nurqamar, S.E., M.M.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Digital Marketing, E-Commerce, Customer Satisfaction, Marketing Management and Tourism Marketing.</t>
-        </is>
-      </c>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="11" t="n"/>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-6040-2293</t>
-        </is>
-      </c>
+      <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
       <c r="M12" s="11" t="inlineStr">
@@ -1201,12 +1197,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Andi Syahida Ulhaq Pasyrib, S.M.</t>
+          <t>Dr. Fahrina Mustafa, SE., M. Si</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1214,12 +1210,20 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E13" s="11" t="n"/>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Digital Marketing, E-Commerce, Customer Satisfaction, Marketing Management and Tourism Marketing.</t>
+        </is>
+      </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-6040-2293</t>
+        </is>
+      </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n"/>
       <c r="M13" s="11" t="inlineStr">
@@ -1234,12 +1238,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>A. Muhammad Ikbal, S.M.</t>
+          <t>Andi Syahida Ulhaq Pasyrib, S.M.</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1265,10 +1269,26 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>A. Muhammad Ikbal, S.M.</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Welcome to the official website of the Market Dynamics Research Group. Our research group members also have a wealth of advisory and consultative experience and a demonstrated commitment to providing objective, technical, and evidence-driven advice.</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
@@ -1276,7 +1296,11 @@
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1465,15 +1489,32 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
